--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592249</v>
+        <v>121592237</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>74707</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593624</v>
+        <v>593965</v>
       </c>
       <c r="R2" t="n">
-        <v>7184680</v>
+        <v>7184404</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592242</v>
+        <v>121592238</v>
       </c>
       <c r="B3" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -804,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593677</v>
+        <v>593966</v>
       </c>
       <c r="R3" t="n">
-        <v>7184592</v>
+        <v>7184400</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592237</v>
+        <v>121592243</v>
       </c>
       <c r="B4" t="n">
-        <v>74707</v>
+        <v>78609</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593965</v>
+        <v>593677</v>
       </c>
       <c r="R4" t="n">
-        <v>7184404</v>
+        <v>7184592</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592252</v>
+        <v>121592250</v>
       </c>
       <c r="B5" t="n">
         <v>57356</v>
@@ -1061,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593625</v>
+        <v>593626</v>
       </c>
       <c r="R5" t="n">
-        <v>7184684</v>
+        <v>7184682</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592247</v>
+        <v>121592242</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1145,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1173,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593634</v>
+        <v>593677</v>
       </c>
       <c r="R6" t="n">
-        <v>7184646</v>
+        <v>7184592</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592251</v>
+        <v>121592252</v>
       </c>
       <c r="B7" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593626</v>
+        <v>593625</v>
       </c>
       <c r="R7" t="n">
-        <v>7184682</v>
+        <v>7184684</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1474,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592255</v>
+        <v>121592256</v>
       </c>
       <c r="B9" t="n">
-        <v>90738</v>
+        <v>74715</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593582</v>
+        <v>593577</v>
       </c>
       <c r="R9" t="n">
-        <v>7184770</v>
+        <v>7184771</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1586,7 +1586,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592250</v>
+        <v>121592239</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593626</v>
+        <v>593783</v>
       </c>
       <c r="R10" t="n">
-        <v>7184682</v>
+        <v>7184462</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1703,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592256</v>
+        <v>121592244</v>
       </c>
       <c r="B11" t="n">
-        <v>74715</v>
+        <v>90738</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1719,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593577</v>
+        <v>593647</v>
       </c>
       <c r="R11" t="n">
-        <v>7184771</v>
+        <v>7184584</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592245</v>
+        <v>121592249</v>
       </c>
       <c r="B13" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,34 +1943,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593625</v>
+        <v>593624</v>
       </c>
       <c r="R13" t="n">
-        <v>7184640</v>
+        <v>7184680</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592239</v>
+        <v>121592255</v>
       </c>
       <c r="B14" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,39 +2060,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593783</v>
+        <v>593582</v>
       </c>
       <c r="R14" t="n">
-        <v>7184462</v>
+        <v>7184770</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592244</v>
+        <v>121592251</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,21 +2172,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593647</v>
+        <v>593626</v>
       </c>
       <c r="R15" t="n">
-        <v>7184584</v>
+        <v>7184682</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2380,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592243</v>
+        <v>121592245</v>
       </c>
       <c r="B17" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,21 +2396,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593677</v>
+        <v>593625</v>
       </c>
       <c r="R17" t="n">
-        <v>7184592</v>
+        <v>7184640</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592241</v>
+        <v>121592257</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,21 +2508,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593711</v>
+        <v>593574</v>
       </c>
       <c r="R18" t="n">
-        <v>7184560</v>
+        <v>7184771</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592238</v>
+        <v>121592241</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,21 +2620,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593966</v>
+        <v>593711</v>
       </c>
       <c r="R19" t="n">
-        <v>7184400</v>
+        <v>7184560</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592257</v>
+        <v>121592247</v>
       </c>
       <c r="B20" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,21 +2732,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593574</v>
+        <v>593634</v>
       </c>
       <c r="R20" t="n">
-        <v>7184771</v>
+        <v>7184646</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592237</v>
+        <v>121592247</v>
       </c>
       <c r="B2" t="n">
-        <v>74707</v>
+        <v>90738</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>308</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593965</v>
+        <v>593634</v>
       </c>
       <c r="R2" t="n">
-        <v>7184404</v>
+        <v>7184646</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592243</v>
+        <v>121592242</v>
       </c>
       <c r="B4" t="n">
-        <v>78609</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592250</v>
+        <v>121592253</v>
       </c>
       <c r="B5" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,16 +1027,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1047,7 +1047,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593626</v>
+        <v>593621</v>
       </c>
       <c r="R5" t="n">
-        <v>7184682</v>
+        <v>7184731</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592242</v>
+        <v>121592245</v>
       </c>
       <c r="B6" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593677</v>
+        <v>593625</v>
       </c>
       <c r="R6" t="n">
-        <v>7184592</v>
+        <v>7184640</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592252</v>
+        <v>121592255</v>
       </c>
       <c r="B7" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593625</v>
+        <v>593582</v>
       </c>
       <c r="R7" t="n">
-        <v>7184684</v>
+        <v>7184770</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592253</v>
+        <v>121592252</v>
       </c>
       <c r="B8" t="n">
-        <v>57372</v>
+        <v>57356</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,16 +1368,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1393,7 +1388,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1402,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593621</v>
+        <v>593625</v>
       </c>
       <c r="R8" t="n">
-        <v>7184731</v>
+        <v>7184684</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1474,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592256</v>
+        <v>121592237</v>
       </c>
       <c r="B9" t="n">
-        <v>74715</v>
+        <v>74707</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1490,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1514,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593577</v>
+        <v>593965</v>
       </c>
       <c r="R9" t="n">
-        <v>7184771</v>
+        <v>7184404</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1559,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1586,7 +1581,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592239</v>
+        <v>121592249</v>
       </c>
       <c r="B10" t="n">
         <v>57356</v>
@@ -1622,7 +1617,7 @@
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593783</v>
+        <v>593624</v>
       </c>
       <c r="R10" t="n">
-        <v>7184462</v>
+        <v>7184680</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592244</v>
+        <v>121592251</v>
       </c>
       <c r="B11" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1719,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1743,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593647</v>
+        <v>593626</v>
       </c>
       <c r="R11" t="n">
-        <v>7184584</v>
+        <v>7184682</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592240</v>
+        <v>121592257</v>
       </c>
       <c r="B12" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1827,25 +1822,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1855,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593713</v>
+        <v>593574</v>
       </c>
       <c r="R12" t="n">
-        <v>7184556</v>
+        <v>7184771</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592249</v>
+        <v>121592248</v>
       </c>
       <c r="B13" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,39 +1938,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593624</v>
+        <v>593634</v>
       </c>
       <c r="R13" t="n">
-        <v>7184680</v>
+        <v>7184646</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +1997,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2007,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2034,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592255</v>
+        <v>121592240</v>
       </c>
       <c r="B14" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,25 +2046,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2074,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593582</v>
+        <v>593713</v>
       </c>
       <c r="R14" t="n">
-        <v>7184770</v>
+        <v>7184556</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592251</v>
+        <v>121592244</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2172,21 +2162,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593626</v>
+        <v>593647</v>
       </c>
       <c r="R15" t="n">
-        <v>7184682</v>
+        <v>7184584</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592248</v>
+        <v>121592256</v>
       </c>
       <c r="B16" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,21 +2274,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593634</v>
+        <v>593577</v>
       </c>
       <c r="R16" t="n">
-        <v>7184646</v>
+        <v>7184771</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592245</v>
+        <v>121592239</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,34 +2386,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593625</v>
+        <v>593783</v>
       </c>
       <c r="R17" t="n">
-        <v>7184640</v>
+        <v>7184462</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592257</v>
+        <v>121592241</v>
       </c>
       <c r="B18" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,21 +2503,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593574</v>
+        <v>593711</v>
       </c>
       <c r="R18" t="n">
-        <v>7184771</v>
+        <v>7184560</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592241</v>
+        <v>121592243</v>
       </c>
       <c r="B19" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,21 +2615,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2644,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593711</v>
+        <v>593677</v>
       </c>
       <c r="R19" t="n">
-        <v>7184560</v>
+        <v>7184592</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592247</v>
+        <v>121592250</v>
       </c>
       <c r="B20" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,34 +2727,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593634</v>
+        <v>593626</v>
       </c>
       <c r="R20" t="n">
-        <v>7184646</v>
+        <v>7184682</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592247</v>
+        <v>121592249</v>
       </c>
       <c r="B2" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593634</v>
+        <v>593624</v>
       </c>
       <c r="R2" t="n">
-        <v>7184646</v>
+        <v>7184680</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +792,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592238</v>
+        <v>121592257</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593966</v>
+        <v>593574</v>
       </c>
       <c r="R3" t="n">
-        <v>7184400</v>
+        <v>7184771</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592242</v>
+        <v>121592244</v>
       </c>
       <c r="B4" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593677</v>
+        <v>593647</v>
       </c>
       <c r="R4" t="n">
-        <v>7184592</v>
+        <v>7184584</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592253</v>
+        <v>121592245</v>
       </c>
       <c r="B5" t="n">
-        <v>57372</v>
+        <v>90738</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593621</v>
+        <v>593625</v>
       </c>
       <c r="R5" t="n">
-        <v>7184731</v>
+        <v>7184640</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592245</v>
+        <v>121592242</v>
       </c>
       <c r="B6" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1140,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593625</v>
+        <v>593677</v>
       </c>
       <c r="R6" t="n">
-        <v>7184640</v>
+        <v>7184592</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1352,7 +1352,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592252</v>
+        <v>121592250</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593625</v>
+        <v>593626</v>
       </c>
       <c r="R8" t="n">
-        <v>7184684</v>
+        <v>7184682</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592237</v>
+        <v>121592239</v>
       </c>
       <c r="B9" t="n">
-        <v>74707</v>
+        <v>57356</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,34 +1485,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593965</v>
+        <v>593783</v>
       </c>
       <c r="R9" t="n">
-        <v>7184404</v>
+        <v>7184462</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592249</v>
+        <v>121592248</v>
       </c>
       <c r="B10" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,39 +1602,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593624</v>
+        <v>593634</v>
       </c>
       <c r="R10" t="n">
-        <v>7184680</v>
+        <v>7184646</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592251</v>
+        <v>121592237</v>
       </c>
       <c r="B11" t="n">
-        <v>78609</v>
+        <v>74707</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,21 +1714,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593626</v>
+        <v>593965</v>
       </c>
       <c r="R11" t="n">
-        <v>7184682</v>
+        <v>7184404</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,7 +1810,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592257</v>
+        <v>121592238</v>
       </c>
       <c r="B12" t="n">
         <v>78609</v>
@@ -1850,10 +1850,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593574</v>
+        <v>593966</v>
       </c>
       <c r="R12" t="n">
-        <v>7184771</v>
+        <v>7184400</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1922,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592248</v>
+        <v>121592253</v>
       </c>
       <c r="B13" t="n">
-        <v>78609</v>
+        <v>57372</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,34 +1938,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593634</v>
+        <v>593621</v>
       </c>
       <c r="R13" t="n">
-        <v>7184646</v>
+        <v>7184731</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1997,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2007,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592240</v>
+        <v>121592243</v>
       </c>
       <c r="B14" t="n">
-        <v>97059</v>
+        <v>78609</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2046,25 +2051,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2074,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593713</v>
+        <v>593677</v>
       </c>
       <c r="R14" t="n">
-        <v>7184556</v>
+        <v>7184592</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592244</v>
+        <v>121592251</v>
       </c>
       <c r="B15" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2162,21 +2167,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593647</v>
+        <v>593626</v>
       </c>
       <c r="R15" t="n">
-        <v>7184584</v>
+        <v>7184682</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592256</v>
+        <v>121592240</v>
       </c>
       <c r="B16" t="n">
-        <v>74715</v>
+        <v>97059</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,25 +2275,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6440</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593577</v>
+        <v>593713</v>
       </c>
       <c r="R16" t="n">
-        <v>7184771</v>
+        <v>7184556</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592239</v>
+        <v>121592241</v>
       </c>
       <c r="B17" t="n">
-        <v>57356</v>
+        <v>90738</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,39 +2391,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593783</v>
+        <v>593711</v>
       </c>
       <c r="R17" t="n">
-        <v>7184462</v>
+        <v>7184560</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592241</v>
+        <v>121592252</v>
       </c>
       <c r="B18" t="n">
-        <v>90738</v>
+        <v>57356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,34 +2503,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593711</v>
+        <v>593625</v>
       </c>
       <c r="R18" t="n">
-        <v>7184560</v>
+        <v>7184684</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592243</v>
+        <v>121592247</v>
       </c>
       <c r="B19" t="n">
-        <v>78609</v>
+        <v>90738</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2620,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593677</v>
+        <v>593634</v>
       </c>
       <c r="R19" t="n">
-        <v>7184592</v>
+        <v>7184646</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592250</v>
+        <v>121592256</v>
       </c>
       <c r="B20" t="n">
-        <v>57356</v>
+        <v>74715</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,39 +2732,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593626</v>
+        <v>593577</v>
       </c>
       <c r="R20" t="n">
-        <v>7184682</v>
+        <v>7184771</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592249</v>
+        <v>121592238</v>
       </c>
       <c r="B2" t="n">
-        <v>57356</v>
+        <v>78609</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593624</v>
+        <v>593966</v>
       </c>
       <c r="R2" t="n">
-        <v>7184680</v>
+        <v>7184400</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592257</v>
+        <v>121592248</v>
       </c>
       <c r="B3" t="n">
         <v>78609</v>
@@ -832,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593574</v>
+        <v>593634</v>
       </c>
       <c r="R3" t="n">
-        <v>7184771</v>
+        <v>7184646</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592244</v>
+        <v>121592242</v>
       </c>
       <c r="B4" t="n">
-        <v>90738</v>
+        <v>97059</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593647</v>
+        <v>593677</v>
       </c>
       <c r="R4" t="n">
-        <v>7184584</v>
+        <v>7184592</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,7 +1011,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592245</v>
+        <v>121592247</v>
       </c>
       <c r="B5" t="n">
         <v>90738</v>
@@ -1056,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593625</v>
+        <v>593634</v>
       </c>
       <c r="R5" t="n">
-        <v>7184640</v>
+        <v>7184646</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592242</v>
+        <v>121592241</v>
       </c>
       <c r="B6" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,25 +1135,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593677</v>
+        <v>593711</v>
       </c>
       <c r="R6" t="n">
-        <v>7184592</v>
+        <v>7184560</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592255</v>
+        <v>121592251</v>
       </c>
       <c r="B7" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593582</v>
+        <v>593626</v>
       </c>
       <c r="R7" t="n">
-        <v>7184770</v>
+        <v>7184682</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592250</v>
+        <v>121592252</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1397,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593626</v>
+        <v>593625</v>
       </c>
       <c r="R8" t="n">
-        <v>7184682</v>
+        <v>7184684</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592248</v>
+        <v>121592256</v>
       </c>
       <c r="B10" t="n">
-        <v>78609</v>
+        <v>74715</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1602,21 +1597,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593634</v>
+        <v>593577</v>
       </c>
       <c r="R10" t="n">
-        <v>7184646</v>
+        <v>7184771</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592237</v>
+        <v>121592240</v>
       </c>
       <c r="B11" t="n">
-        <v>74707</v>
+        <v>97059</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1710,25 +1705,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1738,10 +1733,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593965</v>
+        <v>593713</v>
       </c>
       <c r="R11" t="n">
-        <v>7184404</v>
+        <v>7184556</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1768,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1805,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592238</v>
+        <v>121592237</v>
       </c>
       <c r="B12" t="n">
-        <v>78609</v>
+        <v>74707</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,21 +1821,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1850,10 +1845,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593966</v>
+        <v>593965</v>
       </c>
       <c r="R12" t="n">
-        <v>7184400</v>
+        <v>7184404</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592253</v>
+        <v>121592243</v>
       </c>
       <c r="B13" t="n">
-        <v>57372</v>
+        <v>78609</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1938,39 +1933,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593621</v>
+        <v>593677</v>
       </c>
       <c r="R13" t="n">
-        <v>7184731</v>
+        <v>7184592</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592243</v>
+        <v>121592249</v>
       </c>
       <c r="B14" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,34 +2045,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593677</v>
+        <v>593624</v>
       </c>
       <c r="R14" t="n">
-        <v>7184592</v>
+        <v>7184680</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2146,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592251</v>
+        <v>121592250</v>
       </c>
       <c r="B15" t="n">
-        <v>78609</v>
+        <v>57356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,24 +2162,29 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -2263,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592240</v>
+        <v>121592244</v>
       </c>
       <c r="B16" t="n">
-        <v>97059</v>
+        <v>90738</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,25 +2275,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593713</v>
+        <v>593647</v>
       </c>
       <c r="R16" t="n">
-        <v>7184556</v>
+        <v>7184584</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592241</v>
+        <v>121592257</v>
       </c>
       <c r="B17" t="n">
-        <v>90738</v>
+        <v>78609</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2391,21 +2391,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593711</v>
+        <v>593574</v>
       </c>
       <c r="R17" t="n">
-        <v>7184560</v>
+        <v>7184771</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592252</v>
+        <v>121592253</v>
       </c>
       <c r="B18" t="n">
-        <v>57356</v>
+        <v>57372</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2503,16 +2503,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2523,7 +2523,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593625</v>
+        <v>593621</v>
       </c>
       <c r="R18" t="n">
-        <v>7184684</v>
+        <v>7184731</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,7 +2604,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592247</v>
+        <v>121592245</v>
       </c>
       <c r="B19" t="n">
         <v>90738</v>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593634</v>
+        <v>593625</v>
       </c>
       <c r="R19" t="n">
-        <v>7184646</v>
+        <v>7184640</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592256</v>
+        <v>121592255</v>
       </c>
       <c r="B20" t="n">
-        <v>74715</v>
+        <v>90738</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,21 +2732,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593577</v>
+        <v>593582</v>
       </c>
       <c r="R20" t="n">
-        <v>7184771</v>
+        <v>7184770</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -1347,7 +1347,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592252</v>
+        <v>121592239</v>
       </c>
       <c r="B8" t="n">
         <v>57356</v>
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593625</v>
+        <v>593783</v>
       </c>
       <c r="R8" t="n">
-        <v>7184684</v>
+        <v>7184462</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592239</v>
+        <v>121592252</v>
       </c>
       <c r="B9" t="n">
         <v>57356</v>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593783</v>
+        <v>593625</v>
       </c>
       <c r="R9" t="n">
-        <v>7184462</v>
+        <v>7184684</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592247</v>
+        <v>121592245</v>
       </c>
       <c r="B2" t="n">
         <v>90746</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593634</v>
+        <v>593625</v>
       </c>
       <c r="R2" t="n">
-        <v>7184646</v>
+        <v>7184640</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592239</v>
+        <v>121592253</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593783</v>
+        <v>593621</v>
       </c>
       <c r="R3" t="n">
-        <v>7184462</v>
+        <v>7184731</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592242</v>
+        <v>121592243</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592241</v>
+        <v>121592248</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593711</v>
+        <v>593634</v>
       </c>
       <c r="R5" t="n">
-        <v>7184560</v>
+        <v>7184646</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592243</v>
+        <v>121592237</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>74714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593677</v>
+        <v>593965</v>
       </c>
       <c r="R6" t="n">
-        <v>7184592</v>
+        <v>7184404</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592253</v>
+        <v>121592238</v>
       </c>
       <c r="B7" t="n">
-        <v>57373</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1256,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593621</v>
+        <v>593966</v>
       </c>
       <c r="R7" t="n">
-        <v>7184731</v>
+        <v>7184400</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592251</v>
+        <v>121592255</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1368,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1392,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593626</v>
+        <v>593582</v>
       </c>
       <c r="R8" t="n">
-        <v>7184682</v>
+        <v>7184770</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1464,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592257</v>
+        <v>121592242</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1481,25 +1476,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593574</v>
+        <v>593677</v>
       </c>
       <c r="R9" t="n">
-        <v>7184771</v>
+        <v>7184592</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592240</v>
+        <v>121592256</v>
       </c>
       <c r="B10" t="n">
-        <v>97067</v>
+        <v>74722</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1588,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593713</v>
+        <v>593577</v>
       </c>
       <c r="R10" t="n">
-        <v>7184556</v>
+        <v>7184771</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592249</v>
+        <v>121592241</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,39 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593624</v>
+        <v>593711</v>
       </c>
       <c r="R11" t="n">
-        <v>7184680</v>
+        <v>7184560</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592250</v>
+        <v>121592257</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,39 +1816,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593626</v>
+        <v>593574</v>
       </c>
       <c r="R12" t="n">
-        <v>7184682</v>
+        <v>7184771</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1875,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1885,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1912,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592237</v>
+        <v>121592252</v>
       </c>
       <c r="B13" t="n">
-        <v>74714</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,34 +1928,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593965</v>
+        <v>593625</v>
       </c>
       <c r="R13" t="n">
-        <v>7184404</v>
+        <v>7184684</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,7 +2029,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592255</v>
+        <v>121592244</v>
       </c>
       <c r="B14" t="n">
         <v>90746</v>
@@ -2079,10 +2069,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593582</v>
+        <v>593647</v>
       </c>
       <c r="R14" t="n">
-        <v>7184770</v>
+        <v>7184584</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2104,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2114,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2141,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592245</v>
+        <v>121592250</v>
       </c>
       <c r="B15" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,34 +2157,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593625</v>
+        <v>593626</v>
       </c>
       <c r="R15" t="n">
-        <v>7184640</v>
+        <v>7184682</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592252</v>
+        <v>121592247</v>
       </c>
       <c r="B16" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,39 +2274,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593625</v>
+        <v>593634</v>
       </c>
       <c r="R16" t="n">
-        <v>7184684</v>
+        <v>7184646</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592244</v>
+        <v>121592240</v>
       </c>
       <c r="B17" t="n">
-        <v>90746</v>
+        <v>97067</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2392,25 +2382,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2410,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593647</v>
+        <v>593713</v>
       </c>
       <c r="R17" t="n">
-        <v>7184584</v>
+        <v>7184556</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2445,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2455,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2482,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592238</v>
+        <v>121592249</v>
       </c>
       <c r="B18" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2508,34 +2498,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593966</v>
+        <v>593624</v>
       </c>
       <c r="R18" t="n">
-        <v>7184400</v>
+        <v>7184680</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592248</v>
+        <v>121592239</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,34 +2615,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593634</v>
+        <v>593783</v>
       </c>
       <c r="R19" t="n">
-        <v>7184646</v>
+        <v>7184462</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592256</v>
+        <v>121592251</v>
       </c>
       <c r="B20" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,21 +2732,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593577</v>
+        <v>593626</v>
       </c>
       <c r="R20" t="n">
-        <v>7184771</v>
+        <v>7184682</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -1576,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592256</v>
+        <v>121592241</v>
       </c>
       <c r="B10" t="n">
-        <v>74722</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1592,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6440</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1616,10 +1616,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593577</v>
+        <v>593711</v>
       </c>
       <c r="R10" t="n">
-        <v>7184771</v>
+        <v>7184560</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592241</v>
+        <v>121592256</v>
       </c>
       <c r="B11" t="n">
-        <v>90746</v>
+        <v>74722</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,21 +1704,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1728,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593711</v>
+        <v>593577</v>
       </c>
       <c r="R11" t="n">
-        <v>7184560</v>
+        <v>7184771</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592245</v>
+        <v>121592257</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593625</v>
+        <v>593574</v>
       </c>
       <c r="R2" t="n">
-        <v>7184640</v>
+        <v>7184771</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592253</v>
+        <v>121592237</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>74714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>308</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593621</v>
+        <v>593965</v>
       </c>
       <c r="R3" t="n">
-        <v>7184731</v>
+        <v>7184404</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592243</v>
+        <v>121592250</v>
       </c>
       <c r="B4" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593677</v>
+        <v>593626</v>
       </c>
       <c r="R4" t="n">
-        <v>7184592</v>
+        <v>7184682</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592248</v>
+        <v>121592240</v>
       </c>
       <c r="B5" t="n">
-        <v>78616</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,25 +1028,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593634</v>
+        <v>593713</v>
       </c>
       <c r="R5" t="n">
-        <v>7184646</v>
+        <v>7184556</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592237</v>
+        <v>121592243</v>
       </c>
       <c r="B6" t="n">
-        <v>74714</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593965</v>
+        <v>593677</v>
       </c>
       <c r="R6" t="n">
-        <v>7184404</v>
+        <v>7184592</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592238</v>
+        <v>121592256</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593966</v>
+        <v>593577</v>
       </c>
       <c r="R7" t="n">
-        <v>7184400</v>
+        <v>7184771</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592255</v>
+        <v>121592239</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593582</v>
+        <v>593783</v>
       </c>
       <c r="R8" t="n">
-        <v>7184770</v>
+        <v>7184462</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592242</v>
+        <v>121592248</v>
       </c>
       <c r="B9" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1476,25 +1481,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1504,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593677</v>
+        <v>593634</v>
       </c>
       <c r="R9" t="n">
-        <v>7184592</v>
+        <v>7184646</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592241</v>
+        <v>121592249</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,34 +1597,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593711</v>
+        <v>593624</v>
       </c>
       <c r="R10" t="n">
-        <v>7184560</v>
+        <v>7184680</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1651,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1661,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1688,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592256</v>
+        <v>121592252</v>
       </c>
       <c r="B11" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1704,34 +1714,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593577</v>
+        <v>593625</v>
       </c>
       <c r="R11" t="n">
-        <v>7184771</v>
+        <v>7184684</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592257</v>
+        <v>121592245</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,21 +1831,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1840,10 +1855,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593574</v>
+        <v>593625</v>
       </c>
       <c r="R12" t="n">
-        <v>7184771</v>
+        <v>7184640</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1875,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1885,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1912,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592252</v>
+        <v>121592238</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1928,39 +1943,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593625</v>
+        <v>593966</v>
       </c>
       <c r="R13" t="n">
-        <v>7184684</v>
+        <v>7184400</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,7 +2039,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592244</v>
+        <v>121592247</v>
       </c>
       <c r="B14" t="n">
         <v>90746</v>
@@ -2069,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593647</v>
+        <v>593634</v>
       </c>
       <c r="R14" t="n">
-        <v>7184584</v>
+        <v>7184646</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2104,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2114,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592250</v>
+        <v>121592255</v>
       </c>
       <c r="B15" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2157,39 +2167,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593626</v>
+        <v>593582</v>
       </c>
       <c r="R15" t="n">
-        <v>7184682</v>
+        <v>7184770</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592247</v>
+        <v>121592251</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2274,21 +2279,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593634</v>
+        <v>593626</v>
       </c>
       <c r="R16" t="n">
-        <v>7184646</v>
+        <v>7184682</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,7 +2375,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592240</v>
+        <v>121592242</v>
       </c>
       <c r="B17" t="n">
         <v>97067</v>
@@ -2410,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593713</v>
+        <v>593677</v>
       </c>
       <c r="R17" t="n">
-        <v>7184556</v>
+        <v>7184592</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2445,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2455,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592249</v>
+        <v>121592241</v>
       </c>
       <c r="B18" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2498,39 +2503,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593624</v>
+        <v>593711</v>
       </c>
       <c r="R18" t="n">
-        <v>7184680</v>
+        <v>7184560</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592239</v>
+        <v>121592244</v>
       </c>
       <c r="B19" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,39 +2615,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593783</v>
+        <v>593647</v>
       </c>
       <c r="R19" t="n">
-        <v>7184462</v>
+        <v>7184584</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592251</v>
+        <v>121592253</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,34 +2727,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593626</v>
+        <v>593621</v>
       </c>
       <c r="R20" t="n">
-        <v>7184682</v>
+        <v>7184731</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592250</v>
+        <v>121592240</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,43 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593626</v>
+        <v>593713</v>
       </c>
       <c r="R4" t="n">
-        <v>7184682</v>
+        <v>7184556</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592240</v>
+        <v>121592250</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1023,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593713</v>
+        <v>593626</v>
       </c>
       <c r="R5" t="n">
-        <v>7184556</v>
+        <v>7184682</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592257</v>
+        <v>121592244</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593574</v>
+        <v>593647</v>
       </c>
       <c r="R2" t="n">
-        <v>7184771</v>
+        <v>7184584</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592237</v>
+        <v>121592239</v>
       </c>
       <c r="B3" t="n">
-        <v>74714</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593965</v>
+        <v>593783</v>
       </c>
       <c r="R3" t="n">
-        <v>7184404</v>
+        <v>7184462</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592240</v>
+        <v>121592242</v>
       </c>
       <c r="B4" t="n">
         <v>97067</v>
@@ -939,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593713</v>
+        <v>593677</v>
       </c>
       <c r="R4" t="n">
-        <v>7184556</v>
+        <v>7184592</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592250</v>
+        <v>121592240</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>97067</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,43 +1028,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593626</v>
+        <v>593713</v>
       </c>
       <c r="R5" t="n">
-        <v>7184682</v>
+        <v>7184556</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592243</v>
+        <v>121592255</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593677</v>
+        <v>593582</v>
       </c>
       <c r="R6" t="n">
-        <v>7184592</v>
+        <v>7184770</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592256</v>
+        <v>121592251</v>
       </c>
       <c r="B7" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1280,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593577</v>
+        <v>593626</v>
       </c>
       <c r="R7" t="n">
-        <v>7184771</v>
+        <v>7184682</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1315,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592239</v>
+        <v>121592237</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>74714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,39 +1368,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593783</v>
+        <v>593965</v>
       </c>
       <c r="R8" t="n">
-        <v>7184462</v>
+        <v>7184404</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1427,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1437,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,7 +1464,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592248</v>
+        <v>121592257</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1509,10 +1504,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593634</v>
+        <v>593574</v>
       </c>
       <c r="R9" t="n">
-        <v>7184646</v>
+        <v>7184771</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1539,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1549,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1576,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592249</v>
+        <v>121592248</v>
       </c>
       <c r="B10" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,39 +1592,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593624</v>
+        <v>593634</v>
       </c>
       <c r="R10" t="n">
-        <v>7184680</v>
+        <v>7184646</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1688,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592252</v>
+        <v>121592238</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,39 +1704,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593625</v>
+        <v>593966</v>
       </c>
       <c r="R11" t="n">
-        <v>7184684</v>
+        <v>7184400</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1763,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1773,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1800,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592245</v>
+        <v>121592253</v>
       </c>
       <c r="B12" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1816,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593625</v>
+        <v>593621</v>
       </c>
       <c r="R12" t="n">
-        <v>7184640</v>
+        <v>7184731</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1880,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1890,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1917,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592238</v>
+        <v>121592256</v>
       </c>
       <c r="B13" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,21 +1933,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1967,10 +1957,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593966</v>
+        <v>593577</v>
       </c>
       <c r="R13" t="n">
-        <v>7184400</v>
+        <v>7184771</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1992,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2002,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2029,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592247</v>
+        <v>121592249</v>
       </c>
       <c r="B14" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,34 +2045,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593634</v>
+        <v>593624</v>
       </c>
       <c r="R14" t="n">
-        <v>7184646</v>
+        <v>7184680</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2109,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2119,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,7 +2146,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592255</v>
+        <v>121592245</v>
       </c>
       <c r="B15" t="n">
         <v>90746</v>
@@ -2191,10 +2186,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593582</v>
+        <v>593625</v>
       </c>
       <c r="R15" t="n">
-        <v>7184770</v>
+        <v>7184640</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2221,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2231,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2258,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592251</v>
+        <v>121592241</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,21 +2274,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2298,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593626</v>
+        <v>593711</v>
       </c>
       <c r="R16" t="n">
-        <v>7184682</v>
+        <v>7184560</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,7 +2333,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2343,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592242</v>
+        <v>121592250</v>
       </c>
       <c r="B17" t="n">
-        <v>97067</v>
+        <v>57357</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,38 +2382,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593677</v>
+        <v>593626</v>
       </c>
       <c r="R17" t="n">
-        <v>7184592</v>
+        <v>7184682</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,7 +2487,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592241</v>
+        <v>121592247</v>
       </c>
       <c r="B18" t="n">
         <v>90746</v>
@@ -2527,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593711</v>
+        <v>593634</v>
       </c>
       <c r="R18" t="n">
-        <v>7184560</v>
+        <v>7184646</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592244</v>
+        <v>121592243</v>
       </c>
       <c r="B19" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2615,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593647</v>
+        <v>593677</v>
       </c>
       <c r="R19" t="n">
-        <v>7184584</v>
+        <v>7184592</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2711,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592253</v>
+        <v>121592252</v>
       </c>
       <c r="B20" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,16 +2727,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2747,7 +2747,7 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593621</v>
+        <v>593625</v>
       </c>
       <c r="R20" t="n">
-        <v>7184731</v>
+        <v>7184684</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592244</v>
+        <v>121592252</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593647</v>
+        <v>593625</v>
       </c>
       <c r="R2" t="n">
-        <v>7184584</v>
+        <v>7184684</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592239</v>
+        <v>121592248</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593783</v>
+        <v>593634</v>
       </c>
       <c r="R3" t="n">
-        <v>7184462</v>
+        <v>7184646</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592242</v>
+        <v>121592239</v>
       </c>
       <c r="B4" t="n">
-        <v>97067</v>
+        <v>57357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,38 +916,43 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593677</v>
+        <v>593783</v>
       </c>
       <c r="R4" t="n">
-        <v>7184592</v>
+        <v>7184462</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1021,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592240</v>
+        <v>121592249</v>
       </c>
       <c r="B5" t="n">
-        <v>97067</v>
+        <v>57357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1028,38 +1033,43 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593713</v>
+        <v>593624</v>
       </c>
       <c r="R5" t="n">
-        <v>7184556</v>
+        <v>7184680</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592255</v>
+        <v>121592257</v>
       </c>
       <c r="B6" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1178,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593582</v>
+        <v>593574</v>
       </c>
       <c r="R6" t="n">
-        <v>7184770</v>
+        <v>7184771</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592251</v>
+        <v>121592250</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,24 +1266,29 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1352,10 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592237</v>
+        <v>121592243</v>
       </c>
       <c r="B8" t="n">
-        <v>74714</v>
+        <v>78616</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,21 +1383,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1392,10 +1407,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593965</v>
+        <v>593677</v>
       </c>
       <c r="R8" t="n">
-        <v>7184404</v>
+        <v>7184592</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1427,7 +1442,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1437,7 +1452,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1464,7 +1479,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592257</v>
+        <v>121592238</v>
       </c>
       <c r="B9" t="n">
         <v>78616</v>
@@ -1504,10 +1519,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593574</v>
+        <v>593966</v>
       </c>
       <c r="R9" t="n">
-        <v>7184771</v>
+        <v>7184400</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1539,7 +1554,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1549,7 +1564,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1576,10 +1591,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592248</v>
+        <v>121592247</v>
       </c>
       <c r="B10" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1592,21 +1607,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1688,7 +1703,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592238</v>
+        <v>121592251</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1728,10 +1743,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593966</v>
+        <v>593626</v>
       </c>
       <c r="R11" t="n">
-        <v>7184400</v>
+        <v>7184682</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1763,7 +1778,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1773,7 +1788,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1800,10 +1815,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592253</v>
+        <v>121592256</v>
       </c>
       <c r="B12" t="n">
-        <v>57373</v>
+        <v>74722</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1816,39 +1831,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6440</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593621</v>
+        <v>593577</v>
       </c>
       <c r="R12" t="n">
-        <v>7184731</v>
+        <v>7184771</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1880,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1890,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1917,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592256</v>
+        <v>121592237</v>
       </c>
       <c r="B13" t="n">
-        <v>74722</v>
+        <v>74714</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1933,21 +1943,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6440</v>
+        <v>308</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1957,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593577</v>
+        <v>593965</v>
       </c>
       <c r="R13" t="n">
-        <v>7184771</v>
+        <v>7184404</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -1992,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2002,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2029,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592249</v>
+        <v>121592253</v>
       </c>
       <c r="B14" t="n">
-        <v>57357</v>
+        <v>57373</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2045,16 +2055,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2074,10 +2084,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593624</v>
+        <v>593621</v>
       </c>
       <c r="R14" t="n">
-        <v>7184680</v>
+        <v>7184731</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2109,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2119,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592245</v>
+        <v>121592242</v>
       </c>
       <c r="B15" t="n">
-        <v>90746</v>
+        <v>97067</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2158,25 +2168,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2186,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593625</v>
+        <v>593677</v>
       </c>
       <c r="R15" t="n">
-        <v>7184640</v>
+        <v>7184592</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2221,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2231,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592241</v>
+        <v>121592240</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>97067</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2270,25 +2280,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2298,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593711</v>
+        <v>593713</v>
       </c>
       <c r="R16" t="n">
-        <v>7184560</v>
+        <v>7184556</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2333,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2343,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592250</v>
+        <v>121592244</v>
       </c>
       <c r="B17" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2386,39 +2396,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593626</v>
+        <v>593647</v>
       </c>
       <c r="R17" t="n">
-        <v>7184682</v>
+        <v>7184584</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,7 +2492,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592247</v>
+        <v>121592245</v>
       </c>
       <c r="B18" t="n">
         <v>90746</v>
@@ -2527,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593634</v>
+        <v>593625</v>
       </c>
       <c r="R18" t="n">
-        <v>7184646</v>
+        <v>7184640</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592243</v>
+        <v>121592241</v>
       </c>
       <c r="B19" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,21 +2620,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2639,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593677</v>
+        <v>593711</v>
       </c>
       <c r="R19" t="n">
-        <v>7184592</v>
+        <v>7184560</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2674,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2684,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2711,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592252</v>
+        <v>121592255</v>
       </c>
       <c r="B20" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2727,39 +2732,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593625</v>
+        <v>593582</v>
       </c>
       <c r="R20" t="n">
-        <v>7184684</v>
+        <v>7184770</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592252</v>
+        <v>121592251</v>
       </c>
       <c r="B2" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593625</v>
+        <v>593626</v>
       </c>
       <c r="R2" t="n">
-        <v>7184684</v>
+        <v>7184682</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592248</v>
+        <v>121592253</v>
       </c>
       <c r="B3" t="n">
-        <v>78616</v>
+        <v>57373</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593634</v>
+        <v>593621</v>
       </c>
       <c r="R3" t="n">
-        <v>7184646</v>
+        <v>7184731</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592239</v>
+        <v>121592249</v>
       </c>
       <c r="B4" t="n">
         <v>57357</v>
@@ -940,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +949,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593783</v>
+        <v>593624</v>
       </c>
       <c r="R4" t="n">
-        <v>7184462</v>
+        <v>7184680</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,7 +1021,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592249</v>
+        <v>121592252</v>
       </c>
       <c r="B5" t="n">
         <v>57357</v>
@@ -1057,7 +1057,7 @@
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593624</v>
+        <v>593625</v>
       </c>
       <c r="R5" t="n">
-        <v>7184680</v>
+        <v>7184684</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592257</v>
+        <v>121592256</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>74722</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1154,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593574</v>
+        <v>593577</v>
       </c>
       <c r="R6" t="n">
         <v>7184771</v>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592250</v>
+        <v>121592243</v>
       </c>
       <c r="B7" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,39 +1266,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593626</v>
+        <v>593677</v>
       </c>
       <c r="R7" t="n">
-        <v>7184682</v>
+        <v>7184592</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1330,7 +1325,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1340,7 +1335,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,10 +1362,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592243</v>
+        <v>121592244</v>
       </c>
       <c r="B8" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1383,21 +1378,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1407,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593677</v>
+        <v>593647</v>
       </c>
       <c r="R8" t="n">
-        <v>7184592</v>
+        <v>7184584</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,7 +1437,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1447,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1474,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592238</v>
+        <v>121592255</v>
       </c>
       <c r="B9" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,21 +1490,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1519,10 +1514,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593966</v>
+        <v>593582</v>
       </c>
       <c r="R9" t="n">
-        <v>7184400</v>
+        <v>7184770</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1554,7 +1549,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1564,7 +1559,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,10 +1586,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592247</v>
+        <v>121592237</v>
       </c>
       <c r="B10" t="n">
-        <v>90746</v>
+        <v>74714</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1607,21 +1602,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>308</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1631,10 +1626,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593634</v>
+        <v>593965</v>
       </c>
       <c r="R10" t="n">
-        <v>7184646</v>
+        <v>7184404</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1666,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1676,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1703,7 +1698,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592251</v>
+        <v>121592238</v>
       </c>
       <c r="B11" t="n">
         <v>78616</v>
@@ -1743,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593626</v>
+        <v>593966</v>
       </c>
       <c r="R11" t="n">
-        <v>7184682</v>
+        <v>7184400</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1778,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1788,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1815,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592256</v>
+        <v>121592250</v>
       </c>
       <c r="B12" t="n">
-        <v>74722</v>
+        <v>57357</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1831,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593577</v>
+        <v>593626</v>
       </c>
       <c r="R12" t="n">
-        <v>7184771</v>
+        <v>7184682</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592237</v>
+        <v>121592239</v>
       </c>
       <c r="B13" t="n">
-        <v>74714</v>
+        <v>57357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1943,34 +1943,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593965</v>
+        <v>593783</v>
       </c>
       <c r="R13" t="n">
-        <v>7184404</v>
+        <v>7184462</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +2007,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2017,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2044,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592253</v>
+        <v>121592242</v>
       </c>
       <c r="B14" t="n">
-        <v>57373</v>
+        <v>97067</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2051,43 +2056,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593621</v>
+        <v>593677</v>
       </c>
       <c r="R14" t="n">
-        <v>7184731</v>
+        <v>7184592</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,7 +2156,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592242</v>
+        <v>121592240</v>
       </c>
       <c r="B15" t="n">
         <v>97067</v>
@@ -2196,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593677</v>
+        <v>593713</v>
       </c>
       <c r="R15" t="n">
-        <v>7184592</v>
+        <v>7184556</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592240</v>
+        <v>121592248</v>
       </c>
       <c r="B16" t="n">
-        <v>97067</v>
+        <v>78616</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2280,25 +2280,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593713</v>
+        <v>593634</v>
       </c>
       <c r="R16" t="n">
-        <v>7184556</v>
+        <v>7184646</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,7 +2380,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592244</v>
+        <v>121592241</v>
       </c>
       <c r="B17" t="n">
         <v>90746</v>
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593647</v>
+        <v>593711</v>
       </c>
       <c r="R17" t="n">
-        <v>7184584</v>
+        <v>7184560</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2604,7 +2604,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592241</v>
+        <v>121592247</v>
       </c>
       <c r="B19" t="n">
         <v>90746</v>
@@ -2644,10 +2644,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593711</v>
+        <v>593634</v>
       </c>
       <c r="R19" t="n">
-        <v>7184560</v>
+        <v>7184646</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592255</v>
+        <v>121592257</v>
       </c>
       <c r="B20" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,21 +2732,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593582</v>
+        <v>593574</v>
       </c>
       <c r="R20" t="n">
-        <v>7184770</v>
+        <v>7184771</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592251</v>
+        <v>121592247</v>
       </c>
       <c r="B2" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593626</v>
+        <v>593634</v>
       </c>
       <c r="R2" t="n">
-        <v>7184682</v>
+        <v>7184646</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592253</v>
+        <v>121592239</v>
       </c>
       <c r="B3" t="n">
-        <v>57373</v>
+        <v>57357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593621</v>
+        <v>593783</v>
       </c>
       <c r="R3" t="n">
-        <v>7184731</v>
+        <v>7184462</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592249</v>
+        <v>121592244</v>
       </c>
       <c r="B4" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593624</v>
+        <v>593647</v>
       </c>
       <c r="R4" t="n">
-        <v>7184680</v>
+        <v>7184584</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592252</v>
+        <v>121592245</v>
       </c>
       <c r="B5" t="n">
-        <v>57357</v>
+        <v>90746</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,29 +1032,24 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1069,7 +1059,7 @@
         <v>593625</v>
       </c>
       <c r="R5" t="n">
-        <v>7184684</v>
+        <v>7184640</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592256</v>
+        <v>121592248</v>
       </c>
       <c r="B6" t="n">
-        <v>74722</v>
+        <v>78616</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1178,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593577</v>
+        <v>593634</v>
       </c>
       <c r="R6" t="n">
-        <v>7184771</v>
+        <v>7184646</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1213,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,7 +1240,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592243</v>
+        <v>121592251</v>
       </c>
       <c r="B7" t="n">
         <v>78616</v>
@@ -1290,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593677</v>
+        <v>593626</v>
       </c>
       <c r="R7" t="n">
-        <v>7184592</v>
+        <v>7184682</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1325,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592244</v>
+        <v>121592252</v>
       </c>
       <c r="B8" t="n">
-        <v>90746</v>
+        <v>57357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593647</v>
+        <v>593625</v>
       </c>
       <c r="R8" t="n">
-        <v>7184584</v>
+        <v>7184684</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1437,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1447,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592237</v>
+        <v>121592242</v>
       </c>
       <c r="B10" t="n">
-        <v>74714</v>
+        <v>97067</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1598,25 +1593,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>308</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1626,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593965</v>
+        <v>593677</v>
       </c>
       <c r="R10" t="n">
-        <v>7184404</v>
+        <v>7184592</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592238</v>
+        <v>121592250</v>
       </c>
       <c r="B11" t="n">
-        <v>78616</v>
+        <v>57357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1714,34 +1709,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593966</v>
+        <v>593626</v>
       </c>
       <c r="R11" t="n">
-        <v>7184400</v>
+        <v>7184682</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592250</v>
+        <v>121592243</v>
       </c>
       <c r="B12" t="n">
-        <v>57357</v>
+        <v>78616</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,39 +1826,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593626</v>
+        <v>593677</v>
       </c>
       <c r="R12" t="n">
-        <v>7184682</v>
+        <v>7184592</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1890,7 +1885,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1900,7 +1895,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1927,7 +1922,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592239</v>
+        <v>121592249</v>
       </c>
       <c r="B13" t="n">
         <v>57357</v>
@@ -1963,7 +1958,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1972,10 +1967,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593783</v>
+        <v>593624</v>
       </c>
       <c r="R13" t="n">
-        <v>7184462</v>
+        <v>7184680</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2007,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2017,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2044,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592242</v>
+        <v>121592237</v>
       </c>
       <c r="B14" t="n">
-        <v>97067</v>
+        <v>74714</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2056,25 +2051,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>308</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2084,10 +2079,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593677</v>
+        <v>593965</v>
       </c>
       <c r="R14" t="n">
-        <v>7184592</v>
+        <v>7184404</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2114,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2124,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,10 +2151,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592240</v>
+        <v>121592256</v>
       </c>
       <c r="B15" t="n">
-        <v>97067</v>
+        <v>74722</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2168,25 +2163,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2191,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593713</v>
+        <v>593577</v>
       </c>
       <c r="R15" t="n">
-        <v>7184556</v>
+        <v>7184771</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2226,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2236,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2268,10 +2263,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592248</v>
+        <v>121592241</v>
       </c>
       <c r="B16" t="n">
-        <v>78616</v>
+        <v>90746</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2284,21 +2279,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2308,10 +2303,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593634</v>
+        <v>593711</v>
       </c>
       <c r="R16" t="n">
-        <v>7184646</v>
+        <v>7184560</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2343,7 +2338,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2353,7 +2348,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2380,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592241</v>
+        <v>121592257</v>
       </c>
       <c r="B17" t="n">
-        <v>90746</v>
+        <v>78616</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2396,21 +2391,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2420,10 +2415,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593711</v>
+        <v>593574</v>
       </c>
       <c r="R17" t="n">
-        <v>7184560</v>
+        <v>7184771</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2455,7 +2450,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2465,7 +2460,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2492,10 +2487,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592245</v>
+        <v>121592240</v>
       </c>
       <c r="B18" t="n">
-        <v>90746</v>
+        <v>97067</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2504,25 +2499,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2532,10 +2527,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593625</v>
+        <v>593713</v>
       </c>
       <c r="R18" t="n">
-        <v>7184640</v>
+        <v>7184556</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2567,7 +2562,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2577,7 +2572,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2604,10 +2599,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592247</v>
+        <v>121592253</v>
       </c>
       <c r="B19" t="n">
-        <v>90746</v>
+        <v>57373</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2620,34 +2615,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593634</v>
+        <v>593621</v>
       </c>
       <c r="R19" t="n">
-        <v>7184646</v>
+        <v>7184731</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,7 +2716,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592257</v>
+        <v>121592238</v>
       </c>
       <c r="B20" t="n">
         <v>78616</v>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593574</v>
+        <v>593966</v>
       </c>
       <c r="R20" t="n">
-        <v>7184771</v>
+        <v>7184400</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592247</v>
+        <v>121592248</v>
       </c>
       <c r="B2" t="n">
-        <v>90746</v>
+        <v>78629</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592239</v>
+        <v>121592243</v>
       </c>
       <c r="B3" t="n">
-        <v>57357</v>
+        <v>78629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593783</v>
+        <v>593677</v>
       </c>
       <c r="R3" t="n">
-        <v>7184462</v>
+        <v>7184592</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592244</v>
+        <v>121592241</v>
       </c>
       <c r="B4" t="n">
-        <v>90746</v>
+        <v>90760</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -944,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593647</v>
+        <v>593711</v>
       </c>
       <c r="R4" t="n">
-        <v>7184584</v>
+        <v>7184560</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -979,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:09</t>
+          <t>11:13</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592245</v>
+        <v>121592253</v>
       </c>
       <c r="B5" t="n">
-        <v>90746</v>
+        <v>57381</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593625</v>
+        <v>593621</v>
       </c>
       <c r="R5" t="n">
-        <v>7184640</v>
+        <v>7184731</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592248</v>
+        <v>121592255</v>
       </c>
       <c r="B6" t="n">
-        <v>78616</v>
+        <v>90760</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593634</v>
+        <v>593582</v>
       </c>
       <c r="R6" t="n">
-        <v>7184646</v>
+        <v>7184770</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592251</v>
+        <v>121592249</v>
       </c>
       <c r="B7" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593626</v>
+        <v>593624</v>
       </c>
       <c r="R7" t="n">
-        <v>7184682</v>
+        <v>7184680</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592252</v>
+        <v>121592237</v>
       </c>
       <c r="B8" t="n">
-        <v>57357</v>
+        <v>74727</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>308</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593625</v>
+        <v>593965</v>
       </c>
       <c r="R8" t="n">
-        <v>7184684</v>
+        <v>7184404</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,10 +1469,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592255</v>
+        <v>121592251</v>
       </c>
       <c r="B9" t="n">
-        <v>90746</v>
+        <v>78629</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1485,21 +1485,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593582</v>
+        <v>593626</v>
       </c>
       <c r="R9" t="n">
-        <v>7184770</v>
+        <v>7184682</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592242</v>
+        <v>121592245</v>
       </c>
       <c r="B10" t="n">
-        <v>97067</v>
+        <v>90760</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1593,25 +1593,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1621,10 +1621,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593677</v>
+        <v>593625</v>
       </c>
       <c r="R10" t="n">
-        <v>7184592</v>
+        <v>7184640</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1693,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592250</v>
+        <v>121592252</v>
       </c>
       <c r="B11" t="n">
-        <v>57357</v>
+        <v>57365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593626</v>
+        <v>593625</v>
       </c>
       <c r="R11" t="n">
-        <v>7184682</v>
+        <v>7184684</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1810,10 +1810,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121592243</v>
+        <v>121592250</v>
       </c>
       <c r="B12" t="n">
-        <v>78616</v>
+        <v>57365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1826,34 +1826,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>593677</v>
+        <v>593626</v>
       </c>
       <c r="R12" t="n">
-        <v>7184592</v>
+        <v>7184682</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1885,7 +1890,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1895,7 +1900,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1922,10 +1927,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592249</v>
+        <v>121592242</v>
       </c>
       <c r="B13" t="n">
-        <v>57357</v>
+        <v>97085</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1934,43 +1939,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593624</v>
+        <v>593677</v>
       </c>
       <c r="R13" t="n">
-        <v>7184680</v>
+        <v>7184592</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +2002,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +2012,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,10 +2039,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592237</v>
+        <v>121592239</v>
       </c>
       <c r="B14" t="n">
-        <v>74714</v>
+        <v>57365</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2055,34 +2055,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>308</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593965</v>
+        <v>593783</v>
       </c>
       <c r="R14" t="n">
-        <v>7184404</v>
+        <v>7184462</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2114,7 +2119,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2124,7 +2129,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2151,10 +2156,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592256</v>
+        <v>121592238</v>
       </c>
       <c r="B15" t="n">
-        <v>74722</v>
+        <v>78629</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2167,21 +2172,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2191,10 +2196,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593577</v>
+        <v>593966</v>
       </c>
       <c r="R15" t="n">
-        <v>7184771</v>
+        <v>7184400</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2226,7 +2231,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2236,7 +2241,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2263,10 +2268,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>121592241</v>
+        <v>121592256</v>
       </c>
       <c r="B16" t="n">
-        <v>90746</v>
+        <v>74735</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2279,21 +2284,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>6440</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2303,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>593711</v>
+        <v>593577</v>
       </c>
       <c r="R16" t="n">
-        <v>7184560</v>
+        <v>7184771</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2338,7 +2343,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2348,7 +2353,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2375,10 +2380,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>121592257</v>
+        <v>121592240</v>
       </c>
       <c r="B17" t="n">
-        <v>78616</v>
+        <v>97085</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2387,25 +2392,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2415,10 +2420,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>593574</v>
+        <v>593713</v>
       </c>
       <c r="R17" t="n">
-        <v>7184771</v>
+        <v>7184556</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2450,7 +2455,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2460,7 +2465,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:58</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2487,10 +2492,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>121592240</v>
+        <v>121592244</v>
       </c>
       <c r="B18" t="n">
-        <v>97067</v>
+        <v>90760</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2499,25 +2504,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2527,10 +2532,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>593713</v>
+        <v>593647</v>
       </c>
       <c r="R18" t="n">
-        <v>7184556</v>
+        <v>7184584</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2562,7 +2567,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2572,7 +2577,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:09</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,10 +2604,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>121592253</v>
+        <v>121592257</v>
       </c>
       <c r="B19" t="n">
-        <v>57373</v>
+        <v>78629</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2615,39 +2620,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>593621</v>
+        <v>593574</v>
       </c>
       <c r="R19" t="n">
-        <v>7184731</v>
+        <v>7184771</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2679,7 +2679,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2716,10 +2716,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>121592238</v>
+        <v>121592247</v>
       </c>
       <c r="B20" t="n">
-        <v>78616</v>
+        <v>90760</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2732,21 +2732,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>593966</v>
+        <v>593634</v>
       </c>
       <c r="R20" t="n">
-        <v>7184400</v>
+        <v>7184646</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD20" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -1581,10 +1581,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592245</v>
+        <v>121592252</v>
       </c>
       <c r="B10" t="n">
-        <v>90760</v>
+        <v>57365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1597,24 +1597,29 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1624,7 +1629,7 @@
         <v>593625</v>
       </c>
       <c r="R10" t="n">
-        <v>7184640</v>
+        <v>7184684</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1656,7 +1661,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1666,7 +1671,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,10 +1698,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592252</v>
+        <v>121592245</v>
       </c>
       <c r="B11" t="n">
-        <v>57365</v>
+        <v>90760</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1709,29 +1714,24 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
@@ -1741,7 +1741,7 @@
         <v>593625</v>
       </c>
       <c r="R11" t="n">
-        <v>7184684</v>
+        <v>7184640</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1783,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 47932-2024 artfynd.xlsx
+++ b/artfynd/A 47932-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121592248</v>
+        <v>121592237</v>
       </c>
       <c r="B2" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83299</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>308</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Brunpudrad nållav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca gracillima</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>593634</v>
+        <v>593965</v>
       </c>
       <c r="R2" t="n">
-        <v>7184646</v>
+        <v>7184404</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:05</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,19 +782,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121592243</v>
+        <v>121592238</v>
       </c>
       <c r="B3" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>593677</v>
+        <v>593966</v>
       </c>
       <c r="R3" t="n">
-        <v>7184592</v>
+        <v>7184400</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,37 +889,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121592241</v>
+        <v>121592243</v>
       </c>
       <c r="B4" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>593711</v>
+        <v>593677</v>
       </c>
       <c r="R4" t="n">
-        <v>7184560</v>
+        <v>7184592</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -974,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:13</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,55 +996,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121592253</v>
+        <v>121592248</v>
       </c>
       <c r="B5" t="n">
-        <v>57381</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>593621</v>
+        <v>593634</v>
       </c>
       <c r="R5" t="n">
-        <v>7184731</v>
+        <v>7184646</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,37 +1103,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121592255</v>
+        <v>121592251</v>
       </c>
       <c r="B6" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>593582</v>
+        <v>593626</v>
       </c>
       <c r="R6" t="n">
-        <v>7184770</v>
+        <v>7184682</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,55 +1210,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121592249</v>
+        <v>121592257</v>
       </c>
       <c r="B7" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>593624</v>
+        <v>593574</v>
       </c>
       <c r="R7" t="n">
-        <v>7184680</v>
+        <v>7184771</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1320,7 +1280,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1290,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,15 +1317,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121592237</v>
+        <v>121592256</v>
       </c>
       <c r="B8" t="n">
-        <v>74727</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,21 +1328,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>308</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Brunpudrad nållav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca gracillima</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1352,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>593965</v>
+        <v>593577</v>
       </c>
       <c r="R8" t="n">
-        <v>7184404</v>
+        <v>7184771</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1432,7 +1387,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1397,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,50 +1424,50 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121592251</v>
+        <v>121592253</v>
       </c>
       <c r="B9" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>593626</v>
+        <v>593621</v>
       </c>
       <c r="R9" t="n">
-        <v>7184682</v>
+        <v>7184731</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1544,7 +1499,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1554,7 +1509,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1581,15 +1536,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121592252</v>
+        <v>121592239</v>
       </c>
       <c r="B10" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>593625</v>
+        <v>593783</v>
       </c>
       <c r="R10" t="n">
-        <v>7184684</v>
+        <v>7184462</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1661,7 +1611,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1671,7 +1621,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,15 +1648,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121592245</v>
+        <v>121592249</v>
       </c>
       <c r="B11" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1714,34 +1659,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>593625</v>
+        <v>593624</v>
       </c>
       <c r="R11" t="n">
-        <v>7184640</v>
+        <v>7184680</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1773,7 +1723,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1783,7 +1733,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,12 +1763,7 @@
         <v>121592250</v>
       </c>
       <c r="B12" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1927,50 +1872,50 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121592242</v>
+        <v>121592252</v>
       </c>
       <c r="B13" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>593677</v>
+        <v>593625</v>
       </c>
       <c r="R13" t="n">
-        <v>7184592</v>
+        <v>7184684</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2002,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2012,7 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2039,55 +1984,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>121592239</v>
+        <v>121592240</v>
       </c>
       <c r="B14" t="n">
-        <v>57365</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bullersjön, Ås lm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>593783</v>
+        <v>593713</v>
       </c>
       <c r="R14" t="n">
-        <v>7184462</v>
+        <v>7184556</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2119,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2129,7 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:21</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2156,37 +2091,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>121592238</v>
+        <v>121592242</v>
       </c>
       <c r="B15" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2196,10 +2126,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>593966</v>
+        <v>593677</v>
       </c>
       <c r="R15" t="n">
-        <v>7184400</v>
+        <v>7184592</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2231,7 +2161,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2241,7 +2171,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,566 +2195,6 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>121592256</v>
-      </c>
-      <c r="B16" t="n">
-        <v>74735</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>6440</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Vitgrynig nållav</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Chaenotheca subroscida</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>(Eitner) Zahlbr.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>593577</v>
-      </c>
-      <c r="R16" t="n">
-        <v>7184771</v>
-      </c>
-      <c r="S16" t="n">
-        <v>25</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>10:59</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>121592240</v>
-      </c>
-      <c r="B17" t="n">
-        <v>97085</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>593713</v>
-      </c>
-      <c r="R17" t="n">
-        <v>7184556</v>
-      </c>
-      <c r="S17" t="n">
-        <v>25</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>121592244</v>
-      </c>
-      <c r="B18" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E18" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q18" t="n">
-        <v>593647</v>
-      </c>
-      <c r="R18" t="n">
-        <v>7184584</v>
-      </c>
-      <c r="S18" t="n">
-        <v>25</v>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>11:09</t>
-        </is>
-      </c>
-      <c r="AD18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT18" t="inlineStr"/>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>121592257</v>
-      </c>
-      <c r="B19" t="n">
-        <v>78629</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E19" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Alectoria sarmentosa</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q19" t="n">
-        <v>593574</v>
-      </c>
-      <c r="R19" t="n">
-        <v>7184771</v>
-      </c>
-      <c r="S19" t="n">
-        <v>25</v>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>10:58</t>
-        </is>
-      </c>
-      <c r="AD19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT19" t="inlineStr"/>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>121592247</v>
-      </c>
-      <c r="B20" t="n">
-        <v>90760</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E20" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Bullersjön, Ås lm</t>
-        </is>
-      </c>
-      <c r="Q20" t="n">
-        <v>593634</v>
-      </c>
-      <c r="R20" t="n">
-        <v>7184646</v>
-      </c>
-      <c r="S20" t="n">
-        <v>25</v>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>Åsele lappmark</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>Vilhelmina</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>2024-12-13</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>11:05</t>
-        </is>
-      </c>
-      <c r="AD20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT20" t="inlineStr"/>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>Isak Vahlström</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
